--- a/GourmetProject/GameConfig/Datas/tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/tag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>t_fresh</t>
@@ -542,7 +541,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>term_deliciousness</t>
@@ -550,7 +548,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>t_sweet</t>
@@ -581,11 +578,8 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>t_spicy</t>
@@ -616,7 +610,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>term_adjacent</t>
@@ -624,7 +617,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>t_lonely</t>
@@ -655,7 +647,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>term_empty</t>
@@ -663,7 +654,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>t_hearty</t>
@@ -694,11 +684,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>t_feast</t>
@@ -729,11 +716,8 @@
           <t>0.1</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>t_golden</t>
@@ -764,8 +748,76 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t_cell_gold</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>强化·黄金格</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>占据该格的菜品贡献分数 ×1.5。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Inherent</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t_cell_warm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>强化·温补格</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>占据该格的菜品美味度 +3。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Inherent</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/tag.xlsx
+++ b/GourmetProject/GameConfig/Datas/tag.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,101 +466,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>标签ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>标签名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>标签描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>标签分类</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>效果参数</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>关联术语ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>TagCategory</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>TagEffectType</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>t_fresh</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>新鲜</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>结算时美味度 +5。</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Inherent</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>term_deliciousness</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>t_sweet</t>
+          <t>t_fresh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>香甜</t>
+          <t>新鲜</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>结算时本菜品贡献的分数 ×1.5。</t>
+          <t>结算时美味度 +5。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -570,29 +580,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>term_deliciousness</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>t_spicy</t>
+          <t>t_sweet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>麻辣</t>
+          <t>香甜</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>每有一个相邻菜品，美味度 +3。</t>
+          <t>结算时本菜品贡献的分数 ×1.5。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -602,34 +617,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PerAdjacentDish</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>term_adjacent</t>
+          <t>1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>t_lonely</t>
+          <t>t_spicy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>孤食</t>
+          <t>麻辣</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>棋盘上每有一个空位，美味度 +2。</t>
+          <t>每有一个相邻菜品，美味度 +3。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -639,34 +649,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PerEmptyCell</t>
+          <t>PerAdjacentDish</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>term_empty</t>
+          <t>term_adjacent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>t_hearty</t>
+          <t>t_lonely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>扎实</t>
+          <t>孤食</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>本菜品每占用一格，美味度 +2。</t>
+          <t>棋盘上每有一个空位，美味度 +2。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -676,129 +686,131 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PerOccupiedCell</t>
+          <t>PerEmptyCell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>term_empty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>t_feast</t>
+          <t>t_hearty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>盛宴</t>
+          <t>扎实</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>唯一A。棋盘上每有一道菜，本菜品分数 ×1.1。</t>
+          <t>本菜品每占用一格，美味度 +2。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UniqueA</t>
+          <t>Inherent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PerDishOnBoard</t>
+          <t>PerOccupiedCell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
+          <t>t_feast</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>盛宴</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>唯一A。棋盘上每有一道菜，本菜品分数 ×1.1。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UniqueA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PerDishOnBoard</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
           <t>t_golden</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>黄金</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>唯一B。本菜品贡献的分数 ×2。</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>UniqueB</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>AddMult</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t_cell_gold</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>强化·黄金格</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>占据该格的菜品贡献分数 ×1.5。</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Inherent</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>AddMult</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t_cell_warm</t>
+          <t>t_cell_gold</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>强化·温补格</t>
+          <t>强化·黄金格</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>占据该格的菜品美味度 +3。</t>
+          <t>占据该格的菜品贡献分数 ×1.5。</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -808,16 +820,51 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t_cell_warm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>强化·温补格</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>占据该格的菜品美味度 +3。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Inherent</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
